--- a/artifacts/rental-specimen.xlsx
+++ b/artifacts/rental-specimen.xlsx
@@ -5,21 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z004df5r\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z004df5r\Documents\rental_automation_v1\artifacts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58D78FA4-AFCD-47DC-B91C-1D860DC4F2F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A0DA0F-4032-4D82-9E38-5CBAF79EECE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F707AB7-6C03-44A5-BA9A-694DAD01CD38}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{1F707AB7-6C03-44A5-BA9A-694DAD01CD38}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
     <sheet name="Security Deposit" sheetId="3" r:id="rId2"/>
     <sheet name="Lease Rent" sheetId="4" r:id="rId3"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId4"/>
-  </externalReferences>
   <calcPr calcId="191029" concurrentManualCount="12"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -466,7 +463,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -554,7 +551,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -592,53 +588,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Summary"/>
-      <sheetName val="Main"/>
-      <sheetName val="Rent Calculation"/>
-      <sheetName val="Lease Size"/>
-      <sheetName val="FOREX"/>
-      <sheetName val="ROU_WORKING"/>
-      <sheetName val="FY wise Rental"/>
-      <sheetName val="Lease Rent"/>
-      <sheetName val="LARS working"/>
-      <sheetName val="CAPEX and PM"/>
-      <sheetName val="Security Deposit"/>
-      <sheetName val="Opex"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
-        <row r="23">
-          <cell r="F23">
-            <v>9515</v>
-          </cell>
-          <cell r="G23">
-            <v>883.96506874767749</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1104,17 +1053,17 @@
       <c r="C15" s="1"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="59" t="s">
+      <c r="A16" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="5"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="60" t="s">
+      <c r="A17" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="61">
+      <c r="B17" s="60">
         <v>500000</v>
       </c>
       <c r="C17" s="1"/>
@@ -1156,7 +1105,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="18">
-        <f>+B3*'[1]Rent Calculation'!F23/12*33.5</f>
+        <f>+B3*Main!B12/12*33.5</f>
         <v>0</v>
       </c>
       <c r="D3" s="19"/>
@@ -1271,61 +1220,61 @@
       <c r="D11" s="22"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="62" t="s">
+      <c r="A15" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="62" t="s">
+      <c r="B15" s="61" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="62" t="s">
+      <c r="C15" s="61" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="62" t="s">
+      <c r="A16" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="63">
+      <c r="B16" s="62">
         <f>Main!B3</f>
         <v>9515</v>
       </c>
-      <c r="C16" s="64"/>
+      <c r="C16" s="63"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="65" t="s">
+      <c r="A17" s="64" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="66">
+      <c r="B17" s="65">
         <f>IF(B16&lt;50000,82.6,62.72)</f>
         <v>82.6</v>
       </c>
-      <c r="C17" s="67">
+      <c r="C17" s="66">
         <f>B17*10.764</f>
         <v>889.10639999999989</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="62" t="s">
+      <c r="A18" s="61" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="68">
+      <c r="B18" s="67">
         <f>B16*B17</f>
         <v>785939</v>
       </c>
-      <c r="C18" s="69">
+      <c r="C18" s="68">
         <f ca="1">B18/B10</f>
         <v>10915.819444444445</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="62" t="s">
+      <c r="A19" s="61" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="70">
+      <c r="B19" s="69">
         <f ca="1">C18/B16</f>
         <v>1.1472222222222224</v>
       </c>
-      <c r="C19" s="64"/>
+      <c r="C19" s="63"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1380,151 +1329,151 @@
         <v>2026</v>
       </c>
       <c r="H15" s="11">
-        <f ca="1">SUMIF($A$31:$A$1048576,$G15,$D$31:$D$102)</f>
+        <f t="shared" ref="H15:H21" ca="1" si="0">SUMIF($A$31:$A$1048576,$G15,$D$31:$D$102)</f>
         <v>9</v>
       </c>
       <c r="I15" s="11">
-        <f ca="1">SUMIF($A$31:$A$1048576,$G15,$K$31:$K$102)</f>
+        <f t="shared" ref="I15:I21" ca="1" si="1">SUMIF($A$31:$A$1048576,$G15,$K$31:$K$102)</f>
         <v>10276200</v>
       </c>
       <c r="J15" s="11">
-        <f ca="1">SUMIF($A$31:$A$1048576,$G15,$L$31:$L$102)</f>
+        <f t="shared" ref="J15:J21" ca="1" si="2">SUMIF($A$31:$A$1048576,$G15,$L$31:$L$102)</f>
         <v>1325629.7999999998</v>
       </c>
       <c r="K15" s="12">
-        <f ca="1">I15+J15</f>
+        <f t="shared" ref="K15:K21" ca="1" si="3">I15+J15</f>
         <v>11601829.800000001</v>
       </c>
     </row>
     <row r="16" spans="7:11" x14ac:dyDescent="0.35">
       <c r="G16" s="1">
-        <f>G15+1</f>
+        <f t="shared" ref="G16:G21" si="4">G15+1</f>
         <v>2027</v>
       </c>
       <c r="H16" s="11">
-        <f ca="1">SUMIF($A$31:$A$1048576,$G16,$D$31:$D$102)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>12</v>
       </c>
       <c r="I16" s="11">
-        <f ca="1">SUMIF($A$31:$A$1048576,$G16,$K$31:$K$102)</f>
+        <f t="shared" ca="1" si="1"/>
         <v>13701600</v>
       </c>
       <c r="J16" s="11">
-        <f ca="1">SUMIF($A$31:$A$1048576,$G16,$L$31:$L$102)</f>
+        <f t="shared" ca="1" si="2"/>
         <v>1826423.2800000005</v>
       </c>
       <c r="K16" s="12">
-        <f ca="1">I16+J16</f>
+        <f t="shared" ca="1" si="3"/>
         <v>15528023.280000001</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="G17" s="1">
-        <f>G16+1</f>
+        <f t="shared" si="4"/>
         <v>2028</v>
       </c>
       <c r="H17" s="11">
-        <f ca="1">SUMIF($A$31:$A$1048576,$G17,$D$31:$D$102)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>12</v>
       </c>
       <c r="I17" s="11">
-        <f ca="1">SUMIF($A$31:$A$1048576,$G17,$K$31:$K$102)</f>
+        <f t="shared" ca="1" si="1"/>
         <v>13701600</v>
       </c>
       <c r="J17" s="11">
-        <f ca="1">SUMIF($A$31:$A$1048576,$G17,$L$31:$L$102)</f>
+        <f t="shared" ca="1" si="2"/>
         <v>1917744.4440000001</v>
       </c>
       <c r="K17" s="12">
-        <f ca="1">I17+J17</f>
+        <f t="shared" ca="1" si="3"/>
         <v>15619344.444</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="G18" s="1">
-        <f>G17+1</f>
+        <f t="shared" si="4"/>
         <v>2029</v>
       </c>
       <c r="H18" s="11">
-        <f ca="1">SUMIF($A$31:$A$1048576,$G18,$D$31:$D$102)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>12</v>
       </c>
       <c r="I18" s="11">
-        <f ca="1">SUMIF($A$31:$A$1048576,$G18,$K$31:$K$102)</f>
+        <f t="shared" ca="1" si="1"/>
         <v>15243030</v>
       </c>
       <c r="J18" s="11">
-        <f ca="1">SUMIF($A$31:$A$1048576,$G18,$L$31:$L$102)</f>
+        <f t="shared" ca="1" si="2"/>
         <v>2021751.1487250007</v>
       </c>
       <c r="K18" s="12">
-        <f ca="1">I18+J18</f>
+        <f t="shared" ca="1" si="3"/>
         <v>17264781.148724999</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="G19" s="1">
-        <f>G18+1</f>
+        <f t="shared" si="4"/>
         <v>2030</v>
       </c>
       <c r="H19" s="11">
-        <f ca="1">SUMIF($A$31:$A$1048576,$G19,$D$31:$D$102)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>12</v>
       </c>
       <c r="I19" s="11">
-        <f ca="1">SUMIF($A$31:$A$1048576,$G19,$K$31:$K$102)</f>
+        <f t="shared" ca="1" si="1"/>
         <v>15756840</v>
       </c>
       <c r="J19" s="11">
-        <f ca="1">SUMIF($A$31:$A$1048576,$G19,$L$31:$L$102)</f>
+        <f t="shared" ca="1" si="2"/>
         <v>2114313.2495100005</v>
       </c>
       <c r="K19" s="12">
-        <f ca="1">I19+J19</f>
+        <f t="shared" ca="1" si="3"/>
         <v>17871153.249510001</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="G20" s="1">
-        <f>G19+1</f>
+        <f t="shared" si="4"/>
         <v>2031</v>
       </c>
       <c r="H20" s="11">
-        <f ca="1">SUMIF($A$31:$A$1048576,$G20,$D$31:$D$102)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>12</v>
       </c>
       <c r="I20" s="11">
-        <f ca="1">SUMIF($A$31:$A$1048576,$G20,$K$31:$K$102)</f>
+        <f t="shared" ca="1" si="1"/>
         <v>15756840</v>
       </c>
       <c r="J20" s="11">
-        <f ca="1">SUMIF($A$31:$A$1048576,$G20,$L$31:$L$102)</f>
+        <f t="shared" ca="1" si="2"/>
         <v>2220028.9119855007</v>
       </c>
       <c r="K20" s="12">
-        <f ca="1">I20+J20</f>
+        <f t="shared" ca="1" si="3"/>
         <v>17976868.911985502</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="G21" s="1">
-        <f>G20+1</f>
+        <f t="shared" si="4"/>
         <v>2032</v>
       </c>
       <c r="H21" s="11">
-        <f ca="1">SUMIF($A$31:$A$1048576,$G21,$D$31:$D$102)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
       <c r="I21" s="11">
-        <f ca="1">SUMIF($A$31:$A$1048576,$G21,$K$31:$K$102)</f>
+        <f t="shared" ca="1" si="1"/>
         <v>3939210</v>
       </c>
       <c r="J21" s="11">
-        <f ca="1">SUMIF($A$31:$A$1048576,$G21,$L$31:$L$102)</f>
+        <f t="shared" ca="1" si="2"/>
         <v>563958.95748018753</v>
       </c>
       <c r="K21" s="11">
-        <f ca="1">I21+J21</f>
+        <f t="shared" ca="1" si="3"/>
         <v>4503168.9574801875</v>
       </c>
     </row>
@@ -1610,11 +1559,11 @@
         <v>1</v>
       </c>
       <c r="E31" s="28">
-        <f>'[1]Rent Calculation'!$F$23</f>
+        <f>Main!B3</f>
         <v>9515</v>
       </c>
       <c r="F31" s="28">
-        <f>'[1]Rent Calculation'!G23</f>
+        <f>Main!C3</f>
         <v>883.96506874767749</v>
       </c>
       <c r="G31" s="29"/>
@@ -1628,15 +1577,15 @@
         <v>15.48</v>
       </c>
       <c r="K31" s="28">
-        <f t="shared" ref="K31:K94" si="0">H31*E31</f>
+        <f t="shared" ref="K31:K94" si="5">H31*E31</f>
         <v>1141800</v>
       </c>
       <c r="L31" s="38">
-        <f t="shared" ref="L31:L94" si="1">J31*E31</f>
+        <f t="shared" ref="L31:L94" si="6">J31*E31</f>
         <v>147292.20000000001</v>
       </c>
       <c r="M31" s="32">
-        <f t="shared" ref="M31:M36" si="2">I31+K31+L31</f>
+        <f t="shared" ref="M31:M36" si="7">I31+K31+L31</f>
         <v>1289092.2</v>
       </c>
       <c r="N31" s="33"/>
@@ -1673,15 +1622,15 @@
         <v>15.48</v>
       </c>
       <c r="K32" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L32" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>147292.20000000001</v>
       </c>
       <c r="M32" s="40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>1289092.2</v>
       </c>
       <c r="N32" s="41"/>
@@ -1689,7 +1638,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" s="35">
-        <f t="shared" ref="A33:A39" si="3">A32</f>
+        <f t="shared" ref="A33:A39" si="8">A32</f>
         <v>2026</v>
       </c>
       <c r="B33" s="8">
@@ -1704,11 +1653,11 @@
         <v>1</v>
       </c>
       <c r="E33" s="36">
-        <f t="shared" ref="E33:F48" si="4">E32</f>
+        <f t="shared" ref="E33:F48" si="9">E32</f>
         <v>9515</v>
       </c>
       <c r="F33" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>883.96506874767749</v>
       </c>
       <c r="G33" s="37"/>
@@ -1717,19 +1666,19 @@
       </c>
       <c r="I33" s="36"/>
       <c r="J33" s="39">
-        <f t="shared" ref="J33:J42" si="5">J32</f>
+        <f t="shared" ref="J33:J42" si="10">J32</f>
         <v>15.48</v>
       </c>
       <c r="K33" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L33" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>147292.20000000001</v>
       </c>
       <c r="M33" s="40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>1289092.2</v>
       </c>
       <c r="N33" s="41"/>
@@ -1737,7 +1686,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" s="35">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>2026</v>
       </c>
       <c r="B34" s="8">
@@ -1752,11 +1701,11 @@
         <v>1</v>
       </c>
       <c r="E34" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9515</v>
       </c>
       <c r="F34" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>883.96506874767749</v>
       </c>
       <c r="G34" s="37"/>
@@ -1765,19 +1714,19 @@
       </c>
       <c r="I34" s="36"/>
       <c r="J34" s="39">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>15.48</v>
       </c>
       <c r="K34" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L34" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>147292.20000000001</v>
       </c>
       <c r="M34" s="40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>1289092.2</v>
       </c>
       <c r="N34" s="41"/>
@@ -1785,11 +1734,11 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" s="35">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>2026</v>
       </c>
       <c r="B35" s="8">
-        <f t="shared" ref="B35:B36" si="6">C34+1</f>
+        <f t="shared" ref="B35:B36" si="11">C34+1</f>
         <v>46143</v>
       </c>
       <c r="C35" s="8">
@@ -1800,11 +1749,11 @@
         <v>1</v>
       </c>
       <c r="E35" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9515</v>
       </c>
       <c r="F35" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>883.96506874767749</v>
       </c>
       <c r="G35" s="37"/>
@@ -1813,19 +1762,19 @@
       </c>
       <c r="I35" s="36"/>
       <c r="J35" s="39">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>15.48</v>
       </c>
       <c r="K35" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L35" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>147292.20000000001</v>
       </c>
       <c r="M35" s="40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>1289092.2</v>
       </c>
       <c r="N35" s="41"/>
@@ -1833,11 +1782,11 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" s="35">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>2026</v>
       </c>
       <c r="B36" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>46174</v>
       </c>
       <c r="C36" s="8">
@@ -1848,11 +1797,11 @@
         <v>1</v>
       </c>
       <c r="E36" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9515</v>
       </c>
       <c r="F36" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>883.96506874767749</v>
       </c>
       <c r="G36" s="37"/>
@@ -1861,19 +1810,19 @@
       </c>
       <c r="I36" s="36"/>
       <c r="J36" s="39">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>15.48</v>
       </c>
       <c r="K36" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L36" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>147292.20000000001</v>
       </c>
       <c r="M36" s="40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>1289092.2</v>
       </c>
       <c r="N36" s="41"/>
@@ -1881,7 +1830,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" s="35">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>2026</v>
       </c>
       <c r="B37" s="8">
@@ -1896,11 +1845,11 @@
         <v>1</v>
       </c>
       <c r="E37" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9515</v>
       </c>
       <c r="F37" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H37" s="38">
@@ -1908,15 +1857,15 @@
       </c>
       <c r="I37" s="36"/>
       <c r="J37" s="39">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>15.48</v>
       </c>
       <c r="K37" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L37" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>147292.20000000001</v>
       </c>
       <c r="M37" s="40">
@@ -1928,7 +1877,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" s="35">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>2026</v>
       </c>
       <c r="B38" s="8">
@@ -1943,11 +1892,11 @@
         <v>1</v>
       </c>
       <c r="E38" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9515</v>
       </c>
       <c r="F38" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H38" s="38">
@@ -1955,19 +1904,19 @@
       </c>
       <c r="I38" s="36"/>
       <c r="J38" s="39">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>15.48</v>
       </c>
       <c r="K38" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L38" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>147292.20000000001</v>
       </c>
       <c r="M38" s="40">
-        <f t="shared" ref="M38:M101" si="7">I38+K38+L38</f>
+        <f t="shared" ref="M38:M101" si="12">I38+K38+L38</f>
         <v>1289092.2</v>
       </c>
       <c r="N38" s="36"/>
@@ -1975,11 +1924,11 @@
     </row>
     <row r="39" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>2026</v>
       </c>
       <c r="B39" s="44">
-        <f t="shared" ref="B39:B102" si="8">C38+1</f>
+        <f t="shared" ref="B39:B102" si="13">C38+1</f>
         <v>46265</v>
       </c>
       <c r="C39" s="44">
@@ -1990,11 +1939,11 @@
         <v>1</v>
       </c>
       <c r="E39" s="46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9515</v>
       </c>
       <c r="F39" s="46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>883.96506874767749</v>
       </c>
       <c r="G39" s="45"/>
@@ -2003,19 +1952,19 @@
       </c>
       <c r="I39" s="46"/>
       <c r="J39" s="48">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>15.48</v>
       </c>
       <c r="K39" s="46">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L39" s="47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>147292.20000000001</v>
       </c>
       <c r="M39" s="49">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1289092.2</v>
       </c>
       <c r="N39" s="46">
@@ -2033,7 +1982,7 @@
         <v>2027</v>
       </c>
       <c r="B40" s="26">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>46296</v>
       </c>
       <c r="C40" s="26">
@@ -2044,11 +1993,11 @@
         <v>1</v>
       </c>
       <c r="E40" s="28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9515</v>
       </c>
       <c r="F40" s="28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>883.96506874767749</v>
       </c>
       <c r="G40" s="27"/>
@@ -2057,19 +2006,19 @@
       </c>
       <c r="I40" s="28"/>
       <c r="J40" s="31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>15.48</v>
       </c>
       <c r="K40" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L40" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>147292.20000000001</v>
       </c>
       <c r="M40" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1289092.2</v>
       </c>
       <c r="N40" s="28"/>
@@ -2081,7 +2030,7 @@
         <v>2027</v>
       </c>
       <c r="B41" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>46327</v>
       </c>
       <c r="C41" s="8">
@@ -2092,11 +2041,11 @@
         <v>1</v>
       </c>
       <c r="E41" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9515</v>
       </c>
       <c r="F41" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H41" s="38">
@@ -2104,19 +2053,19 @@
       </c>
       <c r="I41" s="36"/>
       <c r="J41" s="39">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>15.48</v>
       </c>
       <c r="K41" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L41" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>147292.20000000001</v>
       </c>
       <c r="M41" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1289092.2</v>
       </c>
       <c r="N41" s="36"/>
@@ -2128,7 +2077,7 @@
         <v>2027</v>
       </c>
       <c r="B42" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>46357</v>
       </c>
       <c r="C42" s="8">
@@ -2139,11 +2088,11 @@
         <v>1</v>
       </c>
       <c r="E42" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9515</v>
       </c>
       <c r="F42" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H42" s="38">
@@ -2151,19 +2100,19 @@
       </c>
       <c r="I42" s="36"/>
       <c r="J42" s="39">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>15.48</v>
       </c>
       <c r="K42" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L42" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>147292.20000000001</v>
       </c>
       <c r="M42" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1289092.2</v>
       </c>
       <c r="N42" s="36"/>
@@ -2175,7 +2124,7 @@
         <v>2027</v>
       </c>
       <c r="B43" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>46388</v>
       </c>
       <c r="C43" s="8">
@@ -2186,11 +2135,11 @@
         <v>1</v>
       </c>
       <c r="E43" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9515</v>
       </c>
       <c r="F43" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H43" s="38">
@@ -2202,15 +2151,15 @@
         <v>15.48</v>
       </c>
       <c r="K43" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L43" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>147292.20000000001</v>
       </c>
       <c r="M43" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1289092.2</v>
       </c>
       <c r="N43" s="36"/>
@@ -2222,7 +2171,7 @@
         <v>2027</v>
       </c>
       <c r="B44" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>46419</v>
       </c>
       <c r="C44" s="8">
@@ -2233,11 +2182,11 @@
         <v>1</v>
       </c>
       <c r="E44" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9515</v>
       </c>
       <c r="F44" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H44" s="38">
@@ -2249,15 +2198,15 @@
         <v>16.254000000000001</v>
       </c>
       <c r="K44" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L44" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>154656.81000000003</v>
       </c>
       <c r="M44" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1296456.81</v>
       </c>
       <c r="N44" s="36"/>
@@ -2265,11 +2214,11 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" s="35">
-        <f t="shared" ref="A45:A51" si="9">A44</f>
+        <f t="shared" ref="A45:A51" si="14">A44</f>
         <v>2027</v>
       </c>
       <c r="B45" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>46447</v>
       </c>
       <c r="C45" s="8">
@@ -2280,11 +2229,11 @@
         <v>1</v>
       </c>
       <c r="E45" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9515</v>
       </c>
       <c r="F45" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H45" s="38">
@@ -2292,19 +2241,19 @@
       </c>
       <c r="I45" s="36"/>
       <c r="J45" s="39">
-        <f t="shared" ref="J45:J55" si="10">J44</f>
+        <f t="shared" ref="J45:J55" si="15">J44</f>
         <v>16.254000000000001</v>
       </c>
       <c r="K45" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L45" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>154656.81000000003</v>
       </c>
       <c r="M45" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1296456.81</v>
       </c>
       <c r="N45" s="36"/>
@@ -2312,11 +2261,11 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" s="35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>2027</v>
       </c>
       <c r="B46" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>46478</v>
       </c>
       <c r="C46" s="8">
@@ -2327,11 +2276,11 @@
         <v>1</v>
       </c>
       <c r="E46" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9515</v>
       </c>
       <c r="F46" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H46" s="38">
@@ -2339,19 +2288,19 @@
       </c>
       <c r="I46" s="36"/>
       <c r="J46" s="39">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
         <v>16.254000000000001</v>
       </c>
       <c r="K46" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L46" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>154656.81000000003</v>
       </c>
       <c r="M46" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1296456.81</v>
       </c>
       <c r="N46" s="36"/>
@@ -2359,11 +2308,11 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" s="35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>2027</v>
       </c>
       <c r="B47" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>46508</v>
       </c>
       <c r="C47" s="8">
@@ -2374,11 +2323,11 @@
         <v>1</v>
       </c>
       <c r="E47" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9515</v>
       </c>
       <c r="F47" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H47" s="38">
@@ -2386,19 +2335,19 @@
       </c>
       <c r="I47" s="36"/>
       <c r="J47" s="39">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
         <v>16.254000000000001</v>
       </c>
       <c r="K47" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L47" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>154656.81000000003</v>
       </c>
       <c r="M47" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1296456.81</v>
       </c>
       <c r="N47" s="36"/>
@@ -2406,11 +2355,11 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" s="35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>2027</v>
       </c>
       <c r="B48" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>46539</v>
       </c>
       <c r="C48" s="8">
@@ -2421,11 +2370,11 @@
         <v>1</v>
       </c>
       <c r="E48" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9515</v>
       </c>
       <c r="F48" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H48" s="38">
@@ -2433,19 +2382,19 @@
       </c>
       <c r="I48" s="36"/>
       <c r="J48" s="39">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
         <v>16.254000000000001</v>
       </c>
       <c r="K48" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L48" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>154656.81000000003</v>
       </c>
       <c r="M48" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1296456.81</v>
       </c>
       <c r="N48" s="36"/>
@@ -2453,11 +2402,11 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" s="35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>2027</v>
       </c>
       <c r="B49" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>46569</v>
       </c>
       <c r="C49" s="8">
@@ -2468,11 +2417,11 @@
         <v>1</v>
       </c>
       <c r="E49" s="36">
-        <f t="shared" ref="E49:F64" si="11">E48</f>
+        <f t="shared" ref="E49:F64" si="16">E48</f>
         <v>9515</v>
       </c>
       <c r="F49" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H49" s="38">
@@ -2480,19 +2429,19 @@
       </c>
       <c r="I49" s="36"/>
       <c r="J49" s="39">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
         <v>16.254000000000001</v>
       </c>
       <c r="K49" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L49" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>154656.81000000003</v>
       </c>
       <c r="M49" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1296456.81</v>
       </c>
       <c r="N49" s="36"/>
@@ -2500,11 +2449,11 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" s="35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>2027</v>
       </c>
       <c r="B50" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>46600</v>
       </c>
       <c r="C50" s="8">
@@ -2515,11 +2464,11 @@
         <v>1</v>
       </c>
       <c r="E50" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>9515</v>
       </c>
       <c r="F50" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H50" s="38">
@@ -2527,19 +2476,19 @@
       </c>
       <c r="I50" s="36"/>
       <c r="J50" s="39">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
         <v>16.254000000000001</v>
       </c>
       <c r="K50" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L50" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>154656.81000000003</v>
       </c>
       <c r="M50" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1296456.81</v>
       </c>
       <c r="N50" s="36"/>
@@ -2547,11 +2496,11 @@
     </row>
     <row r="51" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>2027</v>
       </c>
       <c r="B51" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>46631</v>
       </c>
       <c r="C51" s="44">
@@ -2562,11 +2511,11 @@
         <v>1</v>
       </c>
       <c r="E51" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>9515</v>
       </c>
       <c r="F51" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>883.96506874767749</v>
       </c>
       <c r="G51" s="45"/>
@@ -2575,19 +2524,19 @@
       </c>
       <c r="I51" s="46"/>
       <c r="J51" s="48">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
         <v>16.254000000000001</v>
       </c>
       <c r="K51" s="46">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L51" s="47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>154656.81000000003</v>
       </c>
       <c r="M51" s="49">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1296456.81</v>
       </c>
       <c r="N51" s="46">
@@ -2605,7 +2554,7 @@
         <v>2028</v>
       </c>
       <c r="B52" s="26">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>46661</v>
       </c>
       <c r="C52" s="26">
@@ -2616,11 +2565,11 @@
         <v>1</v>
       </c>
       <c r="E52" s="28">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>9515</v>
       </c>
       <c r="F52" s="28">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>883.96506874767749</v>
       </c>
       <c r="G52" s="27"/>
@@ -2629,19 +2578,19 @@
       </c>
       <c r="I52" s="28"/>
       <c r="J52" s="31">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
         <v>16.254000000000001</v>
       </c>
       <c r="K52" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L52" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>154656.81000000003</v>
       </c>
       <c r="M52" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1296456.81</v>
       </c>
       <c r="N52" s="28"/>
@@ -2653,7 +2602,7 @@
         <v>2028</v>
       </c>
       <c r="B53" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>46692</v>
       </c>
       <c r="C53" s="8">
@@ -2664,11 +2613,11 @@
         <v>1</v>
       </c>
       <c r="E53" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>9515</v>
       </c>
       <c r="F53" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H53" s="38">
@@ -2676,19 +2625,19 @@
       </c>
       <c r="I53" s="36"/>
       <c r="J53" s="39">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
         <v>16.254000000000001</v>
       </c>
       <c r="K53" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L53" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>154656.81000000003</v>
       </c>
       <c r="M53" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1296456.81</v>
       </c>
       <c r="N53" s="36"/>
@@ -2696,11 +2645,11 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A54" s="35">
-        <f t="shared" ref="A54:A63" si="12">A53</f>
+        <f t="shared" ref="A54:A63" si="17">A53</f>
         <v>2028</v>
       </c>
       <c r="B54" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>46722</v>
       </c>
       <c r="C54" s="8">
@@ -2711,11 +2660,11 @@
         <v>1</v>
       </c>
       <c r="E54" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>9515</v>
       </c>
       <c r="F54" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H54" s="38">
@@ -2723,19 +2672,19 @@
       </c>
       <c r="I54" s="36"/>
       <c r="J54" s="39">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
         <v>16.254000000000001</v>
       </c>
       <c r="K54" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L54" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>154656.81000000003</v>
       </c>
       <c r="M54" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1296456.81</v>
       </c>
       <c r="N54" s="36"/>
@@ -2743,11 +2692,11 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A55" s="35">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>2028</v>
       </c>
       <c r="B55" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>46753</v>
       </c>
       <c r="C55" s="8">
@@ -2758,11 +2707,11 @@
         <v>1</v>
       </c>
       <c r="E55" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>9515</v>
       </c>
       <c r="F55" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H55" s="38">
@@ -2770,19 +2719,19 @@
       </c>
       <c r="I55" s="36"/>
       <c r="J55" s="39">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
         <v>16.254000000000001</v>
       </c>
       <c r="K55" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L55" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>154656.81000000003</v>
       </c>
       <c r="M55" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1296456.81</v>
       </c>
       <c r="N55" s="36"/>
@@ -2790,11 +2739,11 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A56" s="35">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>2028</v>
       </c>
       <c r="B56" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>46784</v>
       </c>
       <c r="C56" s="8">
@@ -2805,11 +2754,11 @@
         <v>1</v>
       </c>
       <c r="E56" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>9515</v>
       </c>
       <c r="F56" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H56" s="38">
@@ -2821,15 +2770,15 @@
         <v>17.066700000000001</v>
       </c>
       <c r="K56" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L56" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>162389.65050000002</v>
       </c>
       <c r="M56" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1304189.6505</v>
       </c>
       <c r="N56" s="36"/>
@@ -2837,11 +2786,11 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A57" s="35">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>2028</v>
       </c>
       <c r="B57" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>46813</v>
       </c>
       <c r="C57" s="8">
@@ -2852,11 +2801,11 @@
         <v>1</v>
       </c>
       <c r="E57" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>9515</v>
       </c>
       <c r="F57" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H57" s="38">
@@ -2864,19 +2813,19 @@
       </c>
       <c r="I57" s="36"/>
       <c r="J57" s="39">
-        <f t="shared" ref="J57:J87" si="13">J56</f>
+        <f t="shared" ref="J57:J87" si="18">J56</f>
         <v>17.066700000000001</v>
       </c>
       <c r="K57" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L57" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>162389.65050000002</v>
       </c>
       <c r="M57" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1304189.6505</v>
       </c>
       <c r="N57" s="36"/>
@@ -2884,11 +2833,11 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A58" s="35">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>2028</v>
       </c>
       <c r="B58" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>46844</v>
       </c>
       <c r="C58" s="8">
@@ -2899,11 +2848,11 @@
         <v>1</v>
       </c>
       <c r="E58" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>9515</v>
       </c>
       <c r="F58" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H58" s="38">
@@ -2911,19 +2860,19 @@
       </c>
       <c r="I58" s="36"/>
       <c r="J58" s="39">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>17.066700000000001</v>
       </c>
       <c r="K58" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L58" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>162389.65050000002</v>
       </c>
       <c r="M58" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1304189.6505</v>
       </c>
       <c r="N58" s="36"/>
@@ -2931,11 +2880,11 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A59" s="35">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>2028</v>
       </c>
       <c r="B59" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>46874</v>
       </c>
       <c r="C59" s="8">
@@ -2946,11 +2895,11 @@
         <v>1</v>
       </c>
       <c r="E59" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>9515</v>
       </c>
       <c r="F59" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H59" s="38">
@@ -2958,19 +2907,19 @@
       </c>
       <c r="I59" s="36"/>
       <c r="J59" s="39">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>17.066700000000001</v>
       </c>
       <c r="K59" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L59" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>162389.65050000002</v>
       </c>
       <c r="M59" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1304189.6505</v>
       </c>
       <c r="N59" s="36"/>
@@ -2978,11 +2927,11 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60" s="35">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>2028</v>
       </c>
       <c r="B60" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>46905</v>
       </c>
       <c r="C60" s="8">
@@ -2993,11 +2942,11 @@
         <v>1</v>
       </c>
       <c r="E60" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>9515</v>
       </c>
       <c r="F60" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H60" s="38">
@@ -3005,19 +2954,19 @@
       </c>
       <c r="I60" s="36"/>
       <c r="J60" s="39">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>17.066700000000001</v>
       </c>
       <c r="K60" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L60" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>162389.65050000002</v>
       </c>
       <c r="M60" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1304189.6505</v>
       </c>
       <c r="N60" s="36"/>
@@ -3025,11 +2974,11 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A61" s="35">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>2028</v>
       </c>
       <c r="B61" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>46935</v>
       </c>
       <c r="C61" s="8">
@@ -3040,11 +2989,11 @@
         <v>1</v>
       </c>
       <c r="E61" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>9515</v>
       </c>
       <c r="F61" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H61" s="38">
@@ -3056,15 +3005,15 @@
         <v>17.066700000000001</v>
       </c>
       <c r="K61" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L61" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>162389.65050000002</v>
       </c>
       <c r="M61" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1304189.6505</v>
       </c>
       <c r="N61" s="36"/>
@@ -3072,11 +3021,11 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A62" s="35">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>2028</v>
       </c>
       <c r="B62" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>46966</v>
       </c>
       <c r="C62" s="8">
@@ -3087,11 +3036,11 @@
         <v>1</v>
       </c>
       <c r="E62" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>9515</v>
       </c>
       <c r="F62" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H62" s="38">
@@ -3103,15 +3052,15 @@
         <v>17.066700000000001</v>
       </c>
       <c r="K62" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L62" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>162389.65050000002</v>
       </c>
       <c r="M62" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1304189.6505</v>
       </c>
       <c r="N62" s="36"/>
@@ -3119,11 +3068,11 @@
     </row>
     <row r="63" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="35">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>2028</v>
       </c>
       <c r="B63" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>46997</v>
       </c>
       <c r="C63" s="44">
@@ -3134,11 +3083,11 @@
         <v>1</v>
       </c>
       <c r="E63" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>9515</v>
       </c>
       <c r="F63" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>883.96506874767749</v>
       </c>
       <c r="G63" s="45"/>
@@ -3147,19 +3096,19 @@
       </c>
       <c r="I63" s="46"/>
       <c r="J63" s="48">
-        <f t="shared" ref="J63:J72" si="14">J62</f>
+        <f t="shared" ref="J63:J72" si="19">J62</f>
         <v>17.066700000000001</v>
       </c>
       <c r="K63" s="46">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L63" s="47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>162389.65050000002</v>
       </c>
       <c r="M63" s="49">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1304189.6505</v>
       </c>
       <c r="N63" s="46">
@@ -3177,7 +3126,7 @@
         <v>2029</v>
       </c>
       <c r="B64" s="26">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47027</v>
       </c>
       <c r="C64" s="26">
@@ -3188,11 +3137,11 @@
         <v>1</v>
       </c>
       <c r="E64" s="28">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>9515</v>
       </c>
       <c r="F64" s="28">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>883.96506874767749</v>
       </c>
       <c r="G64" s="27"/>
@@ -3201,19 +3150,19 @@
       </c>
       <c r="I64" s="28"/>
       <c r="J64" s="31">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>17.066700000000001</v>
       </c>
       <c r="K64" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L64" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>162389.65050000002</v>
       </c>
       <c r="M64" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1304189.6505</v>
       </c>
       <c r="N64" s="28"/>
@@ -3225,7 +3174,7 @@
         <v>2029</v>
       </c>
       <c r="B65" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47058</v>
       </c>
       <c r="C65" s="8">
@@ -3236,11 +3185,11 @@
         <v>1</v>
       </c>
       <c r="E65" s="36">
-        <f t="shared" ref="E65:F80" si="15">E64</f>
+        <f t="shared" ref="E65:F80" si="20">E64</f>
         <v>9515</v>
       </c>
       <c r="F65" s="36">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H65" s="38">
@@ -3248,19 +3197,19 @@
       </c>
       <c r="I65" s="36"/>
       <c r="J65" s="39">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>17.066700000000001</v>
       </c>
       <c r="K65" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L65" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>162389.65050000002</v>
       </c>
       <c r="M65" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1304189.6505</v>
       </c>
       <c r="N65" s="36"/>
@@ -3268,11 +3217,11 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A66" s="35">
-        <f t="shared" ref="A66:A75" si="16">A65</f>
+        <f t="shared" ref="A66:A75" si="21">A65</f>
         <v>2029</v>
       </c>
       <c r="B66" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47088</v>
       </c>
       <c r="C66" s="8">
@@ -3283,11 +3232,11 @@
         <v>1</v>
       </c>
       <c r="E66" s="36">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>9515</v>
       </c>
       <c r="F66" s="36">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H66" s="38">
@@ -3295,19 +3244,19 @@
       </c>
       <c r="I66" s="36"/>
       <c r="J66" s="39">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>17.066700000000001</v>
       </c>
       <c r="K66" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1141800</v>
       </c>
       <c r="L66" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>162389.65050000002</v>
       </c>
       <c r="M66" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1304189.6505</v>
       </c>
       <c r="N66" s="36"/>
@@ -3315,11 +3264,11 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A67" s="35">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>2029</v>
       </c>
       <c r="B67" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47119</v>
       </c>
       <c r="C67" s="8">
@@ -3330,11 +3279,11 @@
         <v>1</v>
       </c>
       <c r="E67" s="36">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>9515</v>
       </c>
       <c r="F67" s="36">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H67" s="38">
@@ -3347,15 +3296,15 @@
         <v>17.920035000000002</v>
       </c>
       <c r="K67" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1313070</v>
       </c>
       <c r="L67" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>170509.13302500002</v>
       </c>
       <c r="M67" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1483579.1330250001</v>
       </c>
       <c r="N67" s="36"/>
@@ -3363,11 +3312,11 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A68" s="35">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>2029</v>
       </c>
       <c r="B68" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47150</v>
       </c>
       <c r="C68" s="8">
@@ -3378,11 +3327,11 @@
         <v>1</v>
       </c>
       <c r="E68" s="36">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>9515</v>
       </c>
       <c r="F68" s="36">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H68" s="38">
@@ -3395,15 +3344,15 @@
         <v>17.920035000000002</v>
       </c>
       <c r="K68" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1313070</v>
       </c>
       <c r="L68" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>170509.13302500002</v>
       </c>
       <c r="M68" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1483579.1330250001</v>
       </c>
       <c r="N68" s="36"/>
@@ -3411,11 +3360,11 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69" s="35">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>2029</v>
       </c>
       <c r="B69" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47178</v>
       </c>
       <c r="C69" s="8">
@@ -3426,32 +3375,32 @@
         <v>1</v>
       </c>
       <c r="E69" s="36">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>9515</v>
       </c>
       <c r="F69" s="36">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H69" s="38">
-        <f t="shared" ref="H69:H102" si="17">H68</f>
+        <f t="shared" ref="H69:H102" si="22">H68</f>
         <v>138</v>
       </c>
       <c r="I69" s="36"/>
       <c r="J69" s="39">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>17.920035000000002</v>
       </c>
       <c r="K69" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1313070</v>
       </c>
       <c r="L69" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>170509.13302500002</v>
       </c>
       <c r="M69" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1483579.1330250001</v>
       </c>
       <c r="N69" s="36"/>
@@ -3459,11 +3408,11 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A70" s="35">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>2029</v>
       </c>
       <c r="B70" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47209</v>
       </c>
       <c r="C70" s="8">
@@ -3474,32 +3423,32 @@
         <v>1</v>
       </c>
       <c r="E70" s="36">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>9515</v>
       </c>
       <c r="F70" s="36">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H70" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I70" s="36"/>
       <c r="J70" s="39">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>17.920035000000002</v>
       </c>
       <c r="K70" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1313070</v>
       </c>
       <c r="L70" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>170509.13302500002</v>
       </c>
       <c r="M70" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1483579.1330250001</v>
       </c>
       <c r="N70" s="36"/>
@@ -3507,11 +3456,11 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A71" s="35">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>2029</v>
       </c>
       <c r="B71" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47239</v>
       </c>
       <c r="C71" s="8">
@@ -3522,32 +3471,32 @@
         <v>1</v>
       </c>
       <c r="E71" s="36">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>9515</v>
       </c>
       <c r="F71" s="36">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H71" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I71" s="36"/>
       <c r="J71" s="39">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>17.920035000000002</v>
       </c>
       <c r="K71" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1313070</v>
       </c>
       <c r="L71" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>170509.13302500002</v>
       </c>
       <c r="M71" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1483579.1330250001</v>
       </c>
       <c r="N71" s="36"/>
@@ -3555,11 +3504,11 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A72" s="35">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>2029</v>
       </c>
       <c r="B72" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47270</v>
       </c>
       <c r="C72" s="8">
@@ -3570,32 +3519,32 @@
         <v>1</v>
       </c>
       <c r="E72" s="36">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>9515</v>
       </c>
       <c r="F72" s="36">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H72" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I72" s="36"/>
       <c r="J72" s="39">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>17.920035000000002</v>
       </c>
       <c r="K72" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1313070</v>
       </c>
       <c r="L72" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>170509.13302500002</v>
       </c>
       <c r="M72" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1483579.1330250001</v>
       </c>
       <c r="N72" s="36"/>
@@ -3603,11 +3552,11 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A73" s="35">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>2029</v>
       </c>
       <c r="B73" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47300</v>
       </c>
       <c r="C73" s="8">
@@ -3618,15 +3567,15 @@
         <v>1</v>
       </c>
       <c r="E73" s="36">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>9515</v>
       </c>
       <c r="F73" s="36">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H73" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I73" s="36"/>
@@ -3635,15 +3584,15 @@
         <v>17.920035000000002</v>
       </c>
       <c r="K73" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1313070</v>
       </c>
       <c r="L73" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>170509.13302500002</v>
       </c>
       <c r="M73" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1483579.1330250001</v>
       </c>
       <c r="N73" s="36"/>
@@ -3651,47 +3600,47 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A74" s="35">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>2029</v>
       </c>
       <c r="B74" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47331</v>
       </c>
       <c r="C74" s="8">
-        <f t="shared" ref="C74" si="18">B74+30</f>
+        <f t="shared" ref="C74" si="23">B74+30</f>
         <v>47361</v>
       </c>
       <c r="D74">
         <v>1</v>
       </c>
       <c r="E74" s="36">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>9515</v>
       </c>
       <c r="F74" s="36">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H74" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I74" s="36"/>
       <c r="J74" s="39">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>17.920035000000002</v>
       </c>
       <c r="K74" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1313070</v>
       </c>
       <c r="L74" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>170509.13302500002</v>
       </c>
       <c r="M74" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1483579.1330250001</v>
       </c>
       <c r="N74" s="36"/>
@@ -3699,11 +3648,11 @@
     </row>
     <row r="75" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="43">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>2029</v>
       </c>
       <c r="B75" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47362</v>
       </c>
       <c r="C75" s="44">
@@ -3714,33 +3663,33 @@
         <v>1</v>
       </c>
       <c r="E75" s="46">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>9515</v>
       </c>
       <c r="F75" s="46">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>883.96506874767749</v>
       </c>
       <c r="G75" s="45"/>
       <c r="H75" s="47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I75" s="46"/>
       <c r="J75" s="48">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>17.920035000000002</v>
       </c>
       <c r="K75" s="46">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1313070</v>
       </c>
       <c r="L75" s="47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>170509.13302500002</v>
       </c>
       <c r="M75" s="49">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1483579.1330250001</v>
       </c>
       <c r="N75" s="46">
@@ -3758,7 +3707,7 @@
         <v>2030</v>
       </c>
       <c r="B76" s="26">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47392</v>
       </c>
       <c r="C76" s="26">
@@ -3769,33 +3718,33 @@
         <v>1</v>
       </c>
       <c r="E76" s="28">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>9515</v>
       </c>
       <c r="F76" s="28">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>883.96506874767749</v>
       </c>
       <c r="G76" s="27"/>
       <c r="H76" s="30">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I76" s="28"/>
       <c r="J76" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>17.920035000000002</v>
       </c>
       <c r="K76" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1313070</v>
       </c>
       <c r="L76" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>170509.13302500002</v>
       </c>
       <c r="M76" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1483579.1330250001</v>
       </c>
       <c r="N76" s="28"/>
@@ -3807,7 +3756,7 @@
         <v>2030</v>
       </c>
       <c r="B77" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47423</v>
       </c>
       <c r="C77" s="8">
@@ -3818,32 +3767,32 @@
         <v>1</v>
       </c>
       <c r="E77" s="36">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>9515</v>
       </c>
       <c r="F77" s="36">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H77" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I77" s="36"/>
       <c r="J77" s="39">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>17.920035000000002</v>
       </c>
       <c r="K77" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1313070</v>
       </c>
       <c r="L77" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>170509.13302500002</v>
       </c>
       <c r="M77" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1483579.1330250001</v>
       </c>
       <c r="N77" s="36"/>
@@ -3851,11 +3800,11 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A78" s="35">
-        <f t="shared" ref="A78:A87" si="19">A77</f>
+        <f t="shared" ref="A78:A87" si="24">A77</f>
         <v>2030</v>
       </c>
       <c r="B78" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47453</v>
       </c>
       <c r="C78" s="8">
@@ -3866,32 +3815,32 @@
         <v>1</v>
       </c>
       <c r="E78" s="36">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>9515</v>
       </c>
       <c r="F78" s="36">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H78" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I78" s="36"/>
       <c r="J78" s="39">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>17.920035000000002</v>
       </c>
       <c r="K78" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1313070</v>
       </c>
       <c r="L78" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>170509.13302500002</v>
       </c>
       <c r="M78" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1483579.1330250001</v>
       </c>
       <c r="N78" s="36"/>
@@ -3899,11 +3848,11 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A79" s="35">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>2030</v>
       </c>
       <c r="B79" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47484</v>
       </c>
       <c r="C79" s="8">
@@ -3914,32 +3863,32 @@
         <v>1</v>
       </c>
       <c r="E79" s="36">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>9515</v>
       </c>
       <c r="F79" s="36">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H79" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I79" s="36"/>
       <c r="J79" s="39">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>17.920035000000002</v>
       </c>
       <c r="K79" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1313070</v>
       </c>
       <c r="L79" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>170509.13302500002</v>
       </c>
       <c r="M79" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1483579.1330250001</v>
       </c>
       <c r="N79" s="36"/>
@@ -3947,11 +3896,11 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A80" s="35">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>2030</v>
       </c>
       <c r="B80" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47515</v>
       </c>
       <c r="C80" s="8">
@@ -3962,15 +3911,15 @@
         <v>1</v>
       </c>
       <c r="E80" s="36">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>9515</v>
       </c>
       <c r="F80" s="36">
-        <f t="shared" si="15"/>
+        <f t="shared" si="20"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H80" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I80" s="36"/>
@@ -3979,15 +3928,15 @@
         <v>18.816036750000002</v>
       </c>
       <c r="K80" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1313070</v>
       </c>
       <c r="L80" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>179034.58967625003</v>
       </c>
       <c r="M80" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1492104.58967625</v>
       </c>
       <c r="N80" s="36"/>
@@ -3995,11 +3944,11 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A81" s="35">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>2030</v>
       </c>
       <c r="B81" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47543</v>
       </c>
       <c r="C81" s="8">
@@ -4010,32 +3959,32 @@
         <v>1</v>
       </c>
       <c r="E81" s="36">
-        <f t="shared" ref="E81:F96" si="20">E80</f>
+        <f t="shared" ref="E81:F96" si="25">E80</f>
         <v>9515</v>
       </c>
       <c r="F81" s="36">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H81" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I81" s="36"/>
       <c r="J81" s="39">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>18.816036750000002</v>
       </c>
       <c r="K81" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1313070</v>
       </c>
       <c r="L81" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>179034.58967625003</v>
       </c>
       <c r="M81" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1492104.58967625</v>
       </c>
       <c r="N81" s="36"/>
@@ -4043,11 +3992,11 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A82" s="35">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>2030</v>
       </c>
       <c r="B82" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47574</v>
       </c>
       <c r="C82" s="8">
@@ -4058,32 +4007,32 @@
         <v>1</v>
       </c>
       <c r="E82" s="36">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>9515</v>
       </c>
       <c r="F82" s="36">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H82" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I82" s="36"/>
       <c r="J82" s="39">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>18.816036750000002</v>
       </c>
       <c r="K82" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1313070</v>
       </c>
       <c r="L82" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>179034.58967625003</v>
       </c>
       <c r="M82" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1492104.58967625</v>
       </c>
       <c r="N82" s="36"/>
@@ -4091,11 +4040,11 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A83" s="35">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>2030</v>
       </c>
       <c r="B83" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47604</v>
       </c>
       <c r="C83" s="8">
@@ -4106,32 +4055,32 @@
         <v>1</v>
       </c>
       <c r="E83" s="36">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>9515</v>
       </c>
       <c r="F83" s="36">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H83" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I83" s="36"/>
       <c r="J83" s="39">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>18.816036750000002</v>
       </c>
       <c r="K83" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1313070</v>
       </c>
       <c r="L83" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>179034.58967625003</v>
       </c>
       <c r="M83" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1492104.58967625</v>
       </c>
       <c r="N83" s="36"/>
@@ -4139,11 +4088,11 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A84" s="35">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>2030</v>
       </c>
       <c r="B84" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47635</v>
       </c>
       <c r="C84" s="8">
@@ -4154,32 +4103,32 @@
         <v>1</v>
       </c>
       <c r="E84" s="36">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>9515</v>
       </c>
       <c r="F84" s="36">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H84" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I84" s="36"/>
       <c r="J84" s="39">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>18.816036750000002</v>
       </c>
       <c r="K84" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1313070</v>
       </c>
       <c r="L84" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>179034.58967625003</v>
       </c>
       <c r="M84" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1492104.58967625</v>
       </c>
       <c r="N84" s="36"/>
@@ -4187,47 +4136,47 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A85" s="35">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>2030</v>
       </c>
       <c r="B85" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47665</v>
       </c>
       <c r="C85" s="8">
-        <f t="shared" ref="C85:C90" si="21">B85+30</f>
+        <f t="shared" ref="C85:C90" si="26">B85+30</f>
         <v>47695</v>
       </c>
       <c r="D85">
         <v>1</v>
       </c>
       <c r="E85" s="36">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>9515</v>
       </c>
       <c r="F85" s="36">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H85" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I85" s="36"/>
       <c r="J85" s="39">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>18.816036750000002</v>
       </c>
       <c r="K85" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1313070</v>
       </c>
       <c r="L85" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>179034.58967625003</v>
       </c>
       <c r="M85" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1492104.58967625</v>
       </c>
       <c r="N85" s="36"/>
@@ -4235,47 +4184,47 @@
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A86" s="35">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>2030</v>
       </c>
       <c r="B86" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47696</v>
       </c>
       <c r="C86" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="26"/>
         <v>47726</v>
       </c>
       <c r="D86">
         <v>1</v>
       </c>
       <c r="E86" s="36">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>9515</v>
       </c>
       <c r="F86" s="36">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H86" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I86" s="36"/>
       <c r="J86" s="39">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>18.816036750000002</v>
       </c>
       <c r="K86" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1313070</v>
       </c>
       <c r="L86" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>179034.58967625003</v>
       </c>
       <c r="M86" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1492104.58967625</v>
       </c>
       <c r="N86" s="36"/>
@@ -4283,11 +4232,11 @@
     </row>
     <row r="87" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="43">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>2030</v>
       </c>
       <c r="B87" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47727</v>
       </c>
       <c r="C87" s="44">
@@ -4298,33 +4247,33 @@
         <v>1</v>
       </c>
       <c r="E87" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>9515</v>
       </c>
       <c r="F87" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>883.96506874767749</v>
       </c>
       <c r="G87" s="45"/>
       <c r="H87" s="47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I87" s="46"/>
       <c r="J87" s="48">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>18.816036750000002</v>
       </c>
       <c r="K87" s="46">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1313070</v>
       </c>
       <c r="L87" s="47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>179034.58967625003</v>
       </c>
       <c r="M87" s="49">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1492104.58967625</v>
       </c>
       <c r="N87" s="46">
@@ -4342,27 +4291,27 @@
         <v>2031</v>
       </c>
       <c r="B88" s="26">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47757</v>
       </c>
       <c r="C88" s="26">
-        <f t="shared" si="21"/>
+        <f t="shared" si="26"/>
         <v>47787</v>
       </c>
       <c r="D88" s="27">
         <v>1</v>
       </c>
       <c r="E88" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>9515</v>
       </c>
       <c r="F88" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>883.96506874767749</v>
       </c>
       <c r="G88" s="27"/>
       <c r="H88" s="30">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I88" s="28"/>
@@ -4371,15 +4320,15 @@
         <v>18.816036750000002</v>
       </c>
       <c r="K88" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1313070</v>
       </c>
       <c r="L88" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>179034.58967625003</v>
       </c>
       <c r="M88" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1492104.58967625</v>
       </c>
       <c r="N88" s="28"/>
@@ -4391,7 +4340,7 @@
         <v>2031</v>
       </c>
       <c r="B89" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47788</v>
       </c>
       <c r="C89" s="8">
@@ -4402,32 +4351,32 @@
         <v>1</v>
       </c>
       <c r="E89" s="36">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>9515</v>
       </c>
       <c r="F89" s="36">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H89" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I89" s="36"/>
       <c r="J89" s="39">
-        <f t="shared" ref="J89:J91" si="22">J88</f>
+        <f t="shared" ref="J89:J91" si="27">J88</f>
         <v>18.816036750000002</v>
       </c>
       <c r="K89" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1313070</v>
       </c>
       <c r="L89" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>179034.58967625003</v>
       </c>
       <c r="M89" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1492104.58967625</v>
       </c>
       <c r="N89" s="36"/>
@@ -4435,47 +4384,47 @@
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A90" s="35">
-        <f t="shared" ref="A90:A99" si="23">A89</f>
+        <f t="shared" ref="A90:A99" si="28">A89</f>
         <v>2031</v>
       </c>
       <c r="B90" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47818</v>
       </c>
       <c r="C90" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="26"/>
         <v>47848</v>
       </c>
       <c r="D90">
         <v>1</v>
       </c>
       <c r="E90" s="36">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>9515</v>
       </c>
       <c r="F90" s="36">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H90" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I90" s="36"/>
       <c r="J90" s="39">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>18.816036750000002</v>
       </c>
       <c r="K90" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1313070</v>
       </c>
       <c r="L90" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>179034.58967625003</v>
       </c>
       <c r="M90" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1492104.58967625</v>
       </c>
       <c r="N90" s="36"/>
@@ -4483,11 +4432,11 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A91" s="35">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>2031</v>
       </c>
       <c r="B91" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47849</v>
       </c>
       <c r="C91" s="8">
@@ -4498,32 +4447,32 @@
         <v>1</v>
       </c>
       <c r="E91" s="36">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>9515</v>
       </c>
       <c r="F91" s="36">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H91" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I91" s="36"/>
       <c r="J91" s="39">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>18.816036750000002</v>
       </c>
       <c r="K91" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1313070</v>
       </c>
       <c r="L91" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>179034.58967625003</v>
       </c>
       <c r="M91" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1492104.58967625</v>
       </c>
       <c r="N91" s="36"/>
@@ -4531,11 +4480,11 @@
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A92" s="35">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>2031</v>
       </c>
       <c r="B92" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47880</v>
       </c>
       <c r="C92" s="8">
@@ -4546,15 +4495,15 @@
         <v>1</v>
       </c>
       <c r="E92" s="36">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>9515</v>
       </c>
       <c r="F92" s="36">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H92" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I92" s="36"/>
@@ -4563,15 +4512,15 @@
         <v>19.756838587500003</v>
       </c>
       <c r="K92" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1313070</v>
       </c>
       <c r="L92" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>187986.31916006253</v>
       </c>
       <c r="M92" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1501056.3191600626</v>
       </c>
       <c r="N92" s="36"/>
@@ -4579,11 +4528,11 @@
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A93" s="35">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>2031</v>
       </c>
       <c r="B93" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47908</v>
       </c>
       <c r="C93" s="8">
@@ -4594,32 +4543,32 @@
         <v>1</v>
       </c>
       <c r="E93" s="36">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>9515</v>
       </c>
       <c r="F93" s="36">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H93" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I93" s="36"/>
       <c r="J93" s="39">
-        <f t="shared" ref="J93:J102" si="24">J92</f>
+        <f t="shared" ref="J93:J102" si="29">J92</f>
         <v>19.756838587500003</v>
       </c>
       <c r="K93" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1313070</v>
       </c>
       <c r="L93" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>187986.31916006253</v>
       </c>
       <c r="M93" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1501056.3191600626</v>
       </c>
       <c r="N93" s="36"/>
@@ -4627,11 +4576,11 @@
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A94" s="35">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>2031</v>
       </c>
       <c r="B94" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47939</v>
       </c>
       <c r="C94" s="8">
@@ -4642,32 +4591,32 @@
         <v>1</v>
       </c>
       <c r="E94" s="36">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>9515</v>
       </c>
       <c r="F94" s="36">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H94" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I94" s="36"/>
       <c r="J94" s="39">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>19.756838587500003</v>
       </c>
       <c r="K94" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1313070</v>
       </c>
       <c r="L94" s="38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>187986.31916006253</v>
       </c>
       <c r="M94" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1501056.3191600626</v>
       </c>
       <c r="N94" s="36"/>
@@ -4675,11 +4624,11 @@
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A95" s="35">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>2031</v>
       </c>
       <c r="B95" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>47969</v>
       </c>
       <c r="C95" s="8">
@@ -4690,32 +4639,32 @@
         <v>1</v>
       </c>
       <c r="E95" s="36">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>9515</v>
       </c>
       <c r="F95" s="36">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H95" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I95" s="36"/>
       <c r="J95" s="39">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>19.756838587500003</v>
       </c>
       <c r="K95" s="36">
-        <f t="shared" ref="K95:K102" si="25">H95*E95</f>
+        <f t="shared" ref="K95:K102" si="30">H95*E95</f>
         <v>1313070</v>
       </c>
       <c r="L95" s="38">
-        <f t="shared" ref="L95:L102" si="26">J95*E95</f>
+        <f t="shared" ref="L95:L102" si="31">J95*E95</f>
         <v>187986.31916006253</v>
       </c>
       <c r="M95" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1501056.3191600626</v>
       </c>
       <c r="N95" s="36"/>
@@ -4723,11 +4672,11 @@
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A96" s="35">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>2031</v>
       </c>
       <c r="B96" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>48000</v>
       </c>
       <c r="C96" s="8">
@@ -4738,32 +4687,32 @@
         <v>1</v>
       </c>
       <c r="E96" s="36">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>9515</v>
       </c>
       <c r="F96" s="36">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H96" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I96" s="36"/>
       <c r="J96" s="39">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>19.756838587500003</v>
       </c>
       <c r="K96" s="36">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>1313070</v>
       </c>
       <c r="L96" s="38">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>187986.31916006253</v>
       </c>
       <c r="M96" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1501056.3191600626</v>
       </c>
       <c r="N96" s="36"/>
@@ -4771,47 +4720,47 @@
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A97" s="35">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>2031</v>
       </c>
       <c r="B97" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>48030</v>
       </c>
       <c r="C97" s="8">
-        <f t="shared" ref="C97:C102" si="27">B97+30</f>
+        <f t="shared" ref="C97:C102" si="32">B97+30</f>
         <v>48060</v>
       </c>
       <c r="D97">
         <v>1</v>
       </c>
       <c r="E97" s="36">
-        <f t="shared" ref="E97:F102" si="28">E96</f>
+        <f t="shared" ref="E97:F102" si="33">E96</f>
         <v>9515</v>
       </c>
       <c r="F97" s="36">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H97" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I97" s="36"/>
       <c r="J97" s="39">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>19.756838587500003</v>
       </c>
       <c r="K97" s="36">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>1313070</v>
       </c>
       <c r="L97" s="38">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>187986.31916006253</v>
       </c>
       <c r="M97" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1501056.3191600626</v>
       </c>
       <c r="N97" s="36"/>
@@ -4819,47 +4768,47 @@
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A98" s="35">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>2031</v>
       </c>
       <c r="B98" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>48061</v>
       </c>
       <c r="C98" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>48091</v>
       </c>
       <c r="D98">
         <v>1</v>
       </c>
       <c r="E98" s="36">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>9515</v>
       </c>
       <c r="F98" s="36">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H98" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I98" s="36"/>
       <c r="J98" s="39">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>19.756838587500003</v>
       </c>
       <c r="K98" s="36">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>1313070</v>
       </c>
       <c r="L98" s="38">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>187986.31916006253</v>
       </c>
       <c r="M98" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1501056.3191600626</v>
       </c>
       <c r="N98" s="36"/>
@@ -4867,11 +4816,11 @@
     </row>
     <row r="99" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="43">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
         <v>2031</v>
       </c>
       <c r="B99" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>48092</v>
       </c>
       <c r="C99" s="44">
@@ -4882,33 +4831,33 @@
         <v>1</v>
       </c>
       <c r="E99" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>9515</v>
       </c>
       <c r="F99" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>883.96506874767749</v>
       </c>
       <c r="G99" s="45"/>
       <c r="H99" s="47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I99" s="46"/>
       <c r="J99" s="48">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>19.756838587500003</v>
       </c>
       <c r="K99" s="46">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>1313070</v>
       </c>
       <c r="L99" s="47">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>187986.31916006253</v>
       </c>
       <c r="M99" s="49">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1501056.3191600626</v>
       </c>
       <c r="N99" s="46">
@@ -4926,44 +4875,44 @@
         <v>2032</v>
       </c>
       <c r="B100" s="26">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>48122</v>
       </c>
       <c r="C100" s="26">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>48152</v>
       </c>
       <c r="D100" s="27">
         <v>1</v>
       </c>
       <c r="E100" s="28">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>9515</v>
       </c>
       <c r="F100" s="28">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>883.96506874767749</v>
       </c>
       <c r="G100" s="27"/>
       <c r="H100" s="30">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I100" s="28"/>
       <c r="J100" s="31">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>19.756838587500003</v>
       </c>
       <c r="K100" s="28">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>1313070</v>
       </c>
       <c r="L100" s="30">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>187986.31916006253</v>
       </c>
       <c r="M100" s="32">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1501056.3191600626</v>
       </c>
       <c r="N100" s="28"/>
@@ -4971,11 +4920,11 @@
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A101" s="35">
-        <f t="shared" ref="A101:A102" si="29">A100</f>
+        <f t="shared" ref="A101:A102" si="34">A100</f>
         <v>2032</v>
       </c>
       <c r="B101" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>48153</v>
       </c>
       <c r="C101" s="8">
@@ -4986,32 +4935,32 @@
         <v>1</v>
       </c>
       <c r="E101" s="36">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>9515</v>
       </c>
       <c r="F101" s="36">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>883.96506874767749</v>
       </c>
       <c r="H101" s="38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I101" s="36"/>
       <c r="J101" s="39">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>19.756838587500003</v>
       </c>
       <c r="K101" s="36">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>1313070</v>
       </c>
       <c r="L101" s="38">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>187986.31916006253</v>
       </c>
       <c r="M101" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>1501056.3191600626</v>
       </c>
       <c r="N101" s="36"/>
@@ -5019,48 +4968,48 @@
     </row>
     <row r="102" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="43">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>2032</v>
       </c>
       <c r="B102" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>48183</v>
       </c>
       <c r="C102" s="44">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>48213</v>
       </c>
       <c r="D102" s="45">
         <v>1</v>
       </c>
       <c r="E102" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>9515</v>
       </c>
       <c r="F102" s="46">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>883.96506874767749</v>
       </c>
       <c r="G102" s="45"/>
       <c r="H102" s="47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>138</v>
       </c>
       <c r="I102" s="46"/>
       <c r="J102" s="48">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>19.756838587500003</v>
       </c>
       <c r="K102" s="46">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>1313070</v>
       </c>
       <c r="L102" s="47">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>187986.31916006253</v>
       </c>
       <c r="M102" s="49">
-        <f t="shared" ref="M102" si="30">I102+K102+L102</f>
+        <f t="shared" ref="M102" si="35">I102+K102+L102</f>
         <v>1501056.3191600626</v>
       </c>
       <c r="N102" s="46">
@@ -5073,24 +5022,24 @@
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="K103" s="71">
+      <c r="K103" s="70">
         <f>SUM(K31:K102)</f>
         <v>88375320</v>
       </c>
-      <c r="L103" s="71">
+      <c r="L103" s="70">
         <f>SUM(L31:L102)</f>
         <v>11989849.791700691</v>
       </c>
-      <c r="M103" s="71">
-        <f t="shared" ref="M103:O103" si="31">SUM(M31:M102)</f>
+      <c r="M103" s="70">
+        <f t="shared" ref="M103:O103" si="36">SUM(M31:M102)</f>
         <v>100365169.79170056</v>
       </c>
-      <c r="N103" s="71">
-        <f t="shared" si="31"/>
+      <c r="N103" s="70">
+        <f t="shared" si="36"/>
         <v>88375320</v>
       </c>
-      <c r="O103" s="71">
-        <f t="shared" si="31"/>
+      <c r="O103" s="70">
+        <f t="shared" si="36"/>
         <v>11989849.791700691</v>
       </c>
     </row>
